--- a/rules/CORE-000726/positive/01/data/unit-test-coreid-FB5701-positive_01.xlsx
+++ b/rules/CORE-000726/positive/01/data/unit-test-coreid-FB5701-positive_01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\verisian\core-contributor\rules\CORE-000726\positive\01\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3F927AB-C686-478F-A9DD-95088143E2F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301A29BC-14A7-4C86-887D-C1ABA3B7A585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="89">
   <si>
     <t>Product</t>
   </si>
@@ -280,9 +280,6 @@
   </si>
   <si>
     <t>Evaluator</t>
-  </si>
-  <si>
-    <t>CDISC-TEST</t>
   </si>
   <si>
     <t>CETHNIC</t>
@@ -1141,7 +1138,7 @@
         <v>41</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>65</v>
@@ -1314,8 +1311,8 @@
       </c>
     </row>
     <row r="5" spans="1:10" ht="60" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>85</v>
+      <c r="A5" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="B5" s="13" t="s">
         <v>41</v>
@@ -1324,21 +1321,21 @@
         <v>53</v>
       </c>
       <c r="F5" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G5" s="13" t="s">
         <v>86</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>87</v>
       </c>
       <c r="H5" s="9" t="s">
         <v>59</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>85</v>
+      <c r="A6" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>41</v>
@@ -1347,39 +1344,39 @@
         <v>60</v>
       </c>
       <c r="F6" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G6" s="13" t="s">
         <v>86</v>
-      </c>
-      <c r="G6" s="13" t="s">
-        <v>87</v>
       </c>
       <c r="H6" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>85</v>
+      <c r="A7" s="9" t="s">
+        <v>40</v>
       </c>
       <c r="B7" s="13" t="s">
         <v>41</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F7" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>86</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>87</v>
       </c>
       <c r="H7" s="9" t="s">
         <v>52</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
   </sheetData>
